--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>20.1</v>
+      <c r="D5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>21.6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17">
-        <v>22.1</v>
+      <c r="D17" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20">
-        <v>20.6</v>
+      <c r="D20" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21">
-        <v>20.6</v>
+      <c r="D21" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -694,7 +694,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -805,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>21.8</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -819,8 +819,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>21.5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -861,8 +861,8 @@
       <c r="C34">
         <v>2</v>
       </c>
-      <c r="D34">
-        <v>22.4</v>
+      <c r="D34" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -988,7 +988,7 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1001,8 +1001,8 @@
       <c r="C44">
         <v>12</v>
       </c>
-      <c r="D44" t="s">
-        <v>4</v>
+      <c r="D44">
+        <v>20.7</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1016,7 +1016,7 @@
         <v>13</v>
       </c>
       <c r="D45">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1029,8 +1029,8 @@
       <c r="C46">
         <v>14</v>
       </c>
-      <c r="D46" t="s">
-        <v>4</v>
+      <c r="D46">
+        <v>18.9</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1170,7 +1170,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>19.1</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1198,7 +1198,7 @@
         <v>26</v>
       </c>
       <c r="D58">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1212,7 +1212,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1239,8 +1239,8 @@
       <c r="C61">
         <v>29</v>
       </c>
-      <c r="D61" t="s">
-        <v>4</v>
+      <c r="D61">
+        <v>21.2</v>
       </c>
     </row>
     <row r="62" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>20.1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -694,7 +694,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -861,8 +861,8 @@
       <c r="C34">
         <v>2</v>
       </c>
-      <c r="D34" t="s">
-        <v>4</v>
+      <c r="D34">
+        <v>21.4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -988,7 +988,7 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1016,7 +1016,7 @@
         <v>13</v>
       </c>
       <c r="D45">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1057,8 +1057,8 @@
       <c r="C48">
         <v>16</v>
       </c>
-      <c r="D48" t="s">
-        <v>4</v>
+      <c r="D48">
+        <v>19.8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1071,8 +1071,8 @@
       <c r="C49">
         <v>17</v>
       </c>
-      <c r="D49" t="s">
-        <v>4</v>
+      <c r="D49">
+        <v>20.4</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1099,8 +1099,8 @@
       <c r="C51">
         <v>19</v>
       </c>
-      <c r="D51" t="s">
-        <v>4</v>
+      <c r="D51">
+        <v>19.9</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1170,7 +1170,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>11.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1212,7 +1212,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="60" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>20.6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1170,7 +1170,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1212,7 +1212,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="60" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -1170,7 +1170,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>19</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="57" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Wet_bulb_temp_06h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -623,8 +620,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>21.9</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -679,8 +676,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>20.6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1170,7 +1167,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1198,7 +1195,7 @@
         <v>26</v>
       </c>
       <c r="D58">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1226,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="D60">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="61" spans="1:4">
